--- a/content/post/drafts/season-prediction/men_model-exhaustive-tests-actual_rmse.xlsx
+++ b/content/post/drafts/season-prediction/men_model-exhaustive-tests-actual_rmse.xlsx
@@ -509,25 +509,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>0.119390048106543</v>
+        <v>0.120695724303118</v>
       </c>
       <c r="C5" t="n">
-        <v>0.145225864687624</v>
+        <v>0.143747013350257</v>
       </c>
       <c r="D5" t="n">
-        <v>0.194867857759431</v>
+        <v>0.194482001089381</v>
       </c>
       <c r="E5" t="n">
-        <v>0.142931971586358</v>
+        <v>0.142483744189644</v>
       </c>
       <c r="F5" t="n">
-        <v>0.132351816103564</v>
+        <v>0.134673891405829</v>
       </c>
       <c r="G5" t="n">
-        <v>0.147058559082142</v>
+        <v>0.146614425203087</v>
       </c>
       <c r="H5" t="n">
-        <v>0.146971019554277</v>
+        <v>0.147116133256886</v>
       </c>
     </row>
     <row r="6">
